--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2330-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2330-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AFC1C84-2A87-4CC0-9D0A-3761B070D04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{999D6E25-7A79-4A97-9DD7-1274A606DFF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{DAA1D91F-113B-4324-8C1F-F4999D451161}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{A65F70A7-6B3B-44C0-84A2-4AB4EE5F4542}"/>
   </bookViews>
   <sheets>
     <sheet name="2330-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1636,23 +1636,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C95B665A-C632-4E21-B7EB-26528E899D1B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9342061-FCF9-4288-9DAF-0E2A0401195A}">
   <dimension ref="A1:R70"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1680,7 +1680,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1710,7 +1710,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1806,7 +1806,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1886,7 +1886,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="51">
         <v>2025</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="53">
         <v>2024</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="51">
         <v>2023</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>26</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
         <v>26</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="53">
         <v>2022</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="51">
         <v>2021</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>26</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>26</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>26</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>26</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="53">
         <v>2020</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>26</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>26</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>26</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>26</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="51">
         <v>2019</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>26</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>26</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="53">
         <v>2018</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>3.52</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="51">
         <v>2017</v>
       </c>
@@ -3996,7 +3996,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="53">
         <v>2016</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="51">
         <v>2015</v>
       </c>
@@ -4104,7 +4104,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="53">
         <v>2014</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="51">
         <v>2013</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="53">
         <v>2012</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="51">
         <v>2011</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="53">
         <v>2010</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>4.8899999999999997</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="51">
         <v>2009</v>
       </c>
@@ -4428,7 +4428,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="53">
         <v>2008</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="51">
         <v>2007</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="53">
         <v>2006</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="51">
         <v>2005</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="53">
         <v>2004</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="51">
         <v>2003</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="53">
         <v>2002</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="51">
         <v>2001</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="53">
         <v>2000</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="51">
         <v>1999</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="53">
         <v>1998</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="51">
         <v>1997</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="53">
         <v>1996</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>7.66</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="51">
         <v>1995</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="53">
         <v>1994</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="68" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="51">
         <v>1993</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="53">
         <v>1992</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="51" t="s">
         <v>81</v>
       </c>
